--- a/artfynd/S 705-2023 artfynd.xlsx
+++ b/artfynd/S 705-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72831510</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -905,6 +915,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72831478</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1019,6 +1034,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72831483</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1133,6 +1153,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72831501</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1247,6 +1272,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72831517</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1361,6 +1391,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72831521</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1471,6 +1506,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6945750</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1584,8 +1624,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105407608</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/S 705-2023 artfynd.xlsx
+++ b/artfynd/S 705-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ9"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -804,61 +804,61 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>72831478</v>
+        <v>136116952</v>
       </c>
       <c r="B3" t="n">
-        <v>106401</v>
+        <v>100650</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1885</v>
+        <v>522</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Klockgentiana</t>
+          <t>Sjötåtel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Gentiana pneumonanthe</t>
+          <t>Deschampsia setacea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Huds.) Hack.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Furen, Yxkullsund, Sm</t>
+          <t>Furen, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>447850</v>
+        <v>447904</v>
       </c>
       <c r="R3" t="n">
-        <v>6319765</v>
+        <v>6319684</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -880,17 +880,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Berga</t>
+          <t>Rydaholm</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2018-08-24</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2018-08-24</t>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Strand</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,13 +922,13 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/72831478</t>
+          <t>https://artportalen.se/Sighting/136116952</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>72831483</v>
+        <v>72831478</v>
       </c>
       <c r="B4" t="n">
         <v>106401</v>
@@ -953,7 +958,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -963,7 +968,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
@@ -974,10 +979,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>447867</v>
+        <v>447850</v>
       </c>
       <c r="R4" t="n">
-        <v>6319824</v>
+        <v>6319765</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1036,13 +1041,13 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/72831483</t>
+          <t>https://artportalen.se/Sighting/72831478</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>72831501</v>
+        <v>72831483</v>
       </c>
       <c r="B5" t="n">
         <v>106401</v>
@@ -1072,7 +1077,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1093,10 +1098,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>447669</v>
+        <v>447867</v>
       </c>
       <c r="R5" t="n">
-        <v>6319841</v>
+        <v>6319824</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1155,13 +1160,13 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/72831501</t>
+          <t>https://artportalen.se/Sighting/72831483</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>72831517</v>
+        <v>72831501</v>
       </c>
       <c r="B6" t="n">
         <v>106401</v>
@@ -1191,7 +1196,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1201,7 +1206,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
@@ -1212,10 +1217,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>447598</v>
+        <v>447669</v>
       </c>
       <c r="R6" t="n">
-        <v>6319903</v>
+        <v>6319841</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1274,13 +1279,13 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/72831517</t>
+          <t>https://artportalen.se/Sighting/72831501</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>72831521</v>
+        <v>72831517</v>
       </c>
       <c r="B7" t="n">
         <v>106401</v>
@@ -1310,7 +1315,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>33</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1331,10 +1336,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>447569</v>
+        <v>447598</v>
       </c>
       <c r="R7" t="n">
-        <v>6319950</v>
+        <v>6319903</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1393,57 +1398,70 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/72831521</t>
+          <t>https://artportalen.se/Sighting/72831517</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>6945750</v>
+        <v>72831521</v>
       </c>
       <c r="B8" t="n">
-        <v>100475</v>
+        <v>106401</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>522</v>
+        <v>1885</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sjötåtel</t>
+          <t>Klockgentiana</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Deschampsia setacea</t>
+          <t>Gentiana pneumonanthe</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Huds.) Hack.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Flåren, Söder om Märkesviken, Sm</t>
+          <t>Furen, Yxkullsund, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>445634</v>
+        <v>447569</v>
       </c>
       <c r="R8" t="n">
-        <v>6319272</v>
+        <v>6319950</v>
       </c>
       <c r="S8" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1467,12 +1485,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>1994-09-26</t>
+          <t>2018-08-24</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1994-09-26</t>
+          <t>2018-08-24</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1481,18 +1499,9 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>MARKSLAG</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Sjöstrand</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1508,70 +1517,70 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/6945750</t>
+          <t>https://artportalen.se/Sighting/72831521</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>105407608</v>
+        <v>136117001</v>
       </c>
       <c r="B9" t="n">
-        <v>57144</v>
+        <v>106590</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102613</v>
+        <v>1885</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Klockgentiana</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Gentiana pneumonanthe</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Svenstorp, Yxkullsund, Berga, Sm</t>
+          <t>Furen, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>446565</v>
+        <v>447857</v>
       </c>
       <c r="R9" t="n">
-        <v>6318739</v>
+        <v>6319767</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1595,12 +1604,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2022-12-29</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2022-12-29</t>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Strand</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1609,22 +1623,504 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Hugo Johansson</t>
+          <t>Krister Wahlström</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Hugo Johansson, Anette Johansson</t>
+          <t>Krister Wahlström</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136117001</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>136117026</v>
+      </c>
+      <c r="B10" t="n">
+        <v>106590</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1885</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Klockgentiana</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Gentiana pneumonanthe</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Furen, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>447866</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6319820</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ljungby</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Berga</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Strand</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Krister Wahlström</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Krister Wahlström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136117026</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>136117070</v>
+      </c>
+      <c r="B11" t="n">
+        <v>106590</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1885</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Klockgentiana</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Gentiana pneumonanthe</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Furen, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>447667</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6319840</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ljungby</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Berga</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Strand</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Krister Wahlström</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Krister Wahlström</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136117070</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>6945750</v>
+      </c>
+      <c r="B12" t="n">
+        <v>100475</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>522</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Sjötåtel</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Deschampsia setacea</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Huds.) Hack.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Flåren, Söder om Märkesviken, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>445634</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6319272</v>
+      </c>
+      <c r="S12" t="n">
+        <v>100</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ljungby</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Berga</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>1994-09-26</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>1994-09-26</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>MARKSLAG</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Sjöstrand</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Krister Wahlström</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Krister Wahlström</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6945750</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>105407608</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57144</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>102613</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Orre</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lyrurus tetrix</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Svenstorp, Yxkullsund, Berga, Sm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>446565</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6318739</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ljungby</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Berga</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2022-12-29</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2022-12-29</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Hugo Johansson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Hugo Johansson, Anette Johansson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/105407608</t>
         </is>
@@ -1640,6 +2136,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 705-2023 artfynd.xlsx
+++ b/artfynd/S 705-2023 artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>136116952</v>
       </c>
       <c r="B3" t="n">
-        <v>100650</v>
+        <v>100652</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>136117001</v>
       </c>
       <c r="B9" t="n">
-        <v>106590</v>
+        <v>106592</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>136117026</v>
       </c>
       <c r="B10" t="n">
-        <v>106590</v>
+        <v>106592</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>136117070</v>
       </c>
       <c r="B11" t="n">
-        <v>106590</v>
+        <v>106592</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/S 705-2023 artfynd.xlsx
+++ b/artfynd/S 705-2023 artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>136116952</v>
       </c>
       <c r="B3" t="n">
-        <v>100652</v>
+        <v>100653</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>136117001</v>
       </c>
       <c r="B9" t="n">
-        <v>106592</v>
+        <v>106593</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>136117026</v>
       </c>
       <c r="B10" t="n">
-        <v>106592</v>
+        <v>106593</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>136117070</v>
       </c>
       <c r="B11" t="n">
-        <v>106592</v>
+        <v>106593</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/S 705-2023 artfynd.xlsx
+++ b/artfynd/S 705-2023 artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>136116952</v>
       </c>
       <c r="B3" t="n">
-        <v>100653</v>
+        <v>100654</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>136117001</v>
       </c>
       <c r="B9" t="n">
-        <v>106593</v>
+        <v>106594</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>136117026</v>
       </c>
       <c r="B10" t="n">
-        <v>106593</v>
+        <v>106594</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>136117070</v>
       </c>
       <c r="B11" t="n">
-        <v>106593</v>
+        <v>106594</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/S 705-2023 artfynd.xlsx
+++ b/artfynd/S 705-2023 artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>136116952</v>
       </c>
       <c r="B3" t="n">
-        <v>100654</v>
+        <v>100660</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>136117001</v>
       </c>
       <c r="B9" t="n">
-        <v>106594</v>
+        <v>106600</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>136117026</v>
       </c>
       <c r="B10" t="n">
-        <v>106594</v>
+        <v>106600</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>136117070</v>
       </c>
       <c r="B11" t="n">
-        <v>106594</v>
+        <v>106600</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/S 705-2023 artfynd.xlsx
+++ b/artfynd/S 705-2023 artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>136116952</v>
       </c>
       <c r="B3" t="n">
-        <v>100660</v>
+        <v>100661</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>136117001</v>
       </c>
       <c r="B9" t="n">
-        <v>106600</v>
+        <v>106601</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>136117026</v>
       </c>
       <c r="B10" t="n">
-        <v>106600</v>
+        <v>106601</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>136117070</v>
       </c>
       <c r="B11" t="n">
-        <v>106600</v>
+        <v>106601</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/S 705-2023 artfynd.xlsx
+++ b/artfynd/S 705-2023 artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>136116952</v>
       </c>
       <c r="B3" t="n">
-        <v>100661</v>
+        <v>100672</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>136117001</v>
       </c>
       <c r="B9" t="n">
-        <v>106601</v>
+        <v>106612</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>136117026</v>
       </c>
       <c r="B10" t="n">
-        <v>106601</v>
+        <v>106612</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>136117070</v>
       </c>
       <c r="B11" t="n">
-        <v>106601</v>
+        <v>106612</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/S 705-2023 artfynd.xlsx
+++ b/artfynd/S 705-2023 artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>136116952</v>
       </c>
       <c r="B3" t="n">
-        <v>100672</v>
+        <v>100685</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>136117001</v>
       </c>
       <c r="B9" t="n">
-        <v>106612</v>
+        <v>106625</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>136117026</v>
       </c>
       <c r="B10" t="n">
-        <v>106612</v>
+        <v>106625</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>136117070</v>
       </c>
       <c r="B11" t="n">
-        <v>106612</v>
+        <v>106625</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/S 705-2023 artfynd.xlsx
+++ b/artfynd/S 705-2023 artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>136116952</v>
       </c>
       <c r="B3" t="n">
-        <v>100685</v>
+        <v>100686</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>136117001</v>
       </c>
       <c r="B9" t="n">
-        <v>106625</v>
+        <v>106626</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>136117026</v>
       </c>
       <c r="B10" t="n">
-        <v>106625</v>
+        <v>106626</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>136117070</v>
       </c>
       <c r="B11" t="n">
-        <v>106625</v>
+        <v>106626</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/S 705-2023 artfynd.xlsx
+++ b/artfynd/S 705-2023 artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>136116952</v>
       </c>
       <c r="B3" t="n">
-        <v>100686</v>
+        <v>100699</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>136117001</v>
       </c>
       <c r="B9" t="n">
-        <v>106626</v>
+        <v>106639</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>136117026</v>
       </c>
       <c r="B10" t="n">
-        <v>106626</v>
+        <v>106639</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>136117070</v>
       </c>
       <c r="B11" t="n">
-        <v>106626</v>
+        <v>106639</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/S 705-2023 artfynd.xlsx
+++ b/artfynd/S 705-2023 artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>136116952</v>
       </c>
       <c r="B3" t="n">
-        <v>100699</v>
+        <v>100700</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>136117001</v>
       </c>
       <c r="B9" t="n">
-        <v>106639</v>
+        <v>106640</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>136117026</v>
       </c>
       <c r="B10" t="n">
-        <v>106639</v>
+        <v>106640</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>136117070</v>
       </c>
       <c r="B11" t="n">
-        <v>106639</v>
+        <v>106640</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
